--- a/artfynd/A 64154-2025 artfynd.xlsx
+++ b/artfynd/A 64154-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133655822</v>
+        <v>133655819</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490446</v>
+        <v>490412</v>
       </c>
       <c r="R2" t="n">
-        <v>6781916</v>
+        <v>6781969</v>
       </c>
       <c r="S2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +758,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack med synlig sav högt på tall</t>
+          <t>Rikligt med stor garnlav</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133655819</v>
+        <v>133655822</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,26 +802,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490412</v>
+        <v>490446</v>
       </c>
       <c r="R3" t="n">
-        <v>6781969</v>
+        <v>6781916</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,12 +879,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med stor garnlav</t>
+          <t>Ringhack med synlig sav högt på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +893,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64154-2025 artfynd.xlsx
+++ b/artfynd/A 64154-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133655819</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>133655815</v>
       </c>
       <c r="B5" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>133655817</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>133655821</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64154-2025 artfynd.xlsx
+++ b/artfynd/A 64154-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133655819</v>
+        <v>133655822</v>
       </c>
       <c r="B2" t="n">
-        <v>79334</v>
+        <v>57965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490412</v>
+        <v>490446</v>
       </c>
       <c r="R2" t="n">
-        <v>6781969</v>
+        <v>6781916</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,12 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt med stor garnlav</t>
+          <t>Ringhack med synlig sav högt på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133655822</v>
+        <v>133655819</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>79348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,31 +806,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490446</v>
+        <v>490412</v>
       </c>
       <c r="R3" t="n">
-        <v>6781916</v>
+        <v>6781969</v>
       </c>
       <c r="S3" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,12 +878,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack med synlig sav högt på tall</t>
+          <t>Rikligt med stor garnlav</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,6 +892,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -914,7 +914,7 @@
         <v>133655823</v>
       </c>
       <c r="B4" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>133655815</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>133655817</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>133655816</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>133655821</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64154-2025 artfynd.xlsx
+++ b/artfynd/A 64154-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133655822</v>
+        <v>133655819</v>
       </c>
       <c r="B2" t="n">
-        <v>57965</v>
+        <v>79348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490446</v>
+        <v>490412</v>
       </c>
       <c r="R2" t="n">
-        <v>6781916</v>
+        <v>6781969</v>
       </c>
       <c r="S2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +758,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack med synlig sav högt på tall</t>
+          <t>Rikligt med stor garnlav</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133655819</v>
+        <v>133655822</v>
       </c>
       <c r="B3" t="n">
-        <v>79348</v>
+        <v>57965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,26 +802,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490412</v>
+        <v>490446</v>
       </c>
       <c r="R3" t="n">
-        <v>6781969</v>
+        <v>6781916</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,12 +879,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med stor garnlav</t>
+          <t>Ringhack med synlig sav högt på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +893,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64154-2025 artfynd.xlsx
+++ b/artfynd/A 64154-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133655819</v>
+        <v>133655822</v>
       </c>
       <c r="B2" t="n">
-        <v>79348</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490412</v>
+        <v>490446</v>
       </c>
       <c r="R2" t="n">
-        <v>6781969</v>
+        <v>6781916</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,12 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt med stor garnlav</t>
+          <t>Ringhack med synlig sav högt på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133655822</v>
+        <v>133655819</v>
       </c>
       <c r="B3" t="n">
-        <v>57965</v>
+        <v>79358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,31 +806,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490446</v>
+        <v>490412</v>
       </c>
       <c r="R3" t="n">
-        <v>6781916</v>
+        <v>6781969</v>
       </c>
       <c r="S3" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,12 +878,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack med synlig sav högt på tall</t>
+          <t>Rikligt med stor garnlav</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,6 +892,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>133655815</v>
       </c>
       <c r="B5" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>133655817</v>
       </c>
       <c r="B6" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>133655816</v>
       </c>
       <c r="B7" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>133655821</v>
       </c>
       <c r="B8" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64154-2025 artfynd.xlsx
+++ b/artfynd/A 64154-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133655822</v>
+        <v>133655819</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490446</v>
+        <v>490412</v>
       </c>
       <c r="R2" t="n">
-        <v>6781916</v>
+        <v>6781969</v>
       </c>
       <c r="S2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +758,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack med synlig sav högt på tall</t>
+          <t>Rikligt med stor garnlav</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133655819</v>
+        <v>133655822</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,26 +802,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490412</v>
+        <v>490446</v>
       </c>
       <c r="R3" t="n">
-        <v>6781969</v>
+        <v>6781916</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,12 +879,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med stor garnlav</t>
+          <t>Ringhack med synlig sav högt på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +893,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64154-2025 artfynd.xlsx
+++ b/artfynd/A 64154-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133655819</v>
       </c>
       <c r="B2" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>133655815</v>
       </c>
       <c r="B5" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>133655817</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>133655821</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64154-2025 artfynd.xlsx
+++ b/artfynd/A 64154-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133655822</v>
+        <v>133655819</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490446</v>
+        <v>490412</v>
       </c>
       <c r="R2" t="n">
-        <v>6781916</v>
+        <v>6781969</v>
       </c>
       <c r="S2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +758,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack med synlig sav högt på tall</t>
+          <t>Rikligt med stor garnlav</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133655819</v>
+        <v>133655822</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,26 +802,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490412</v>
+        <v>490446</v>
       </c>
       <c r="R3" t="n">
-        <v>6781969</v>
+        <v>6781916</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,12 +879,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med stor garnlav</t>
+          <t>Ringhack med synlig sav högt på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +893,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64154-2025 artfynd.xlsx
+++ b/artfynd/A 64154-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133655819</v>
       </c>
       <c r="B2" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>133655815</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>133655817</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>133655821</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64154-2025 artfynd.xlsx
+++ b/artfynd/A 64154-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133655819</v>
+        <v>133655815</v>
       </c>
       <c r="B2" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -704,19 +704,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallmorberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490412</v>
+        <v>490438</v>
       </c>
       <c r="R2" t="n">
-        <v>6781969</v>
+        <v>6781764</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med stor garnlav</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,42 +782,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133655822</v>
+        <v>133655817</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490446</v>
+        <v>490424</v>
       </c>
       <c r="R3" t="n">
-        <v>6781916</v>
+        <v>6781823</v>
       </c>
       <c r="S3" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,12 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack med synlig sav högt på tall</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,6 +874,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -911,48 +893,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133655823</v>
+        <v>133655819</v>
       </c>
       <c r="B4" t="n">
-        <v>8460</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallmorberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490449</v>
+        <v>490412</v>
       </c>
       <c r="R4" t="n">
-        <v>6781860</v>
+        <v>6781969</v>
       </c>
       <c r="S4" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +966,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +976,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med stor garnlav</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,14 +1009,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133655815</v>
+        <v>133655821</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1048,16 +1038,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kallmorberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490438</v>
+        <v>490431</v>
       </c>
       <c r="R5" t="n">
-        <v>6781764</v>
+        <v>6781918</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1089,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1092,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt med stor garnlav</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,6 +1106,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1126,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133655817</v>
+        <v>133655816</v>
       </c>
       <c r="B6" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,26 +1136,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1164,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490424</v>
+        <v>490443</v>
       </c>
       <c r="R6" t="n">
-        <v>6781823</v>
+        <v>6781792</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack med synlig sav högt på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,7 +1227,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1237,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133655816</v>
+        <v>133655822</v>
       </c>
       <c r="B7" t="n">
         <v>57975</v>
@@ -1280,13 +1288,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490443</v>
+        <v>490446</v>
       </c>
       <c r="R7" t="n">
-        <v>6781792</v>
+        <v>6781916</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1357,51 +1365,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133655821</v>
+        <v>133655823</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>8460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallmorberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490431</v>
+        <v>490449</v>
       </c>
       <c r="R8" t="n">
-        <v>6781918</v>
+        <v>6781860</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,12 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med stor garnlav</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 64154-2025 artfynd.xlsx
+++ b/artfynd/A 64154-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133655815</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133655817</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133655819</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133655821</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133655816</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1362,6 +1392,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133655822</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,6 +1505,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133655823</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1577,8 +1617,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135086743</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 64154-2025 artfynd.xlsx
+++ b/artfynd/A 64154-2025 artfynd.xlsx
@@ -1516,7 +1516,7 @@
         <v>135086743</v>
       </c>
       <c r="B9" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
